--- a/runs/legacy/season_plan_spond.xlsx
+++ b/runs/legacy/season_plan_spond.xlsx
@@ -20412,38 +20412,38 @@
         <v>46368</v>
       </c>
       <c r="B333" s="5" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C333" s="5" t="n"/>
       <c r="D333" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
+          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker Orange · JU12</t>
+          <t>Frisk Asker · Frisk Asker 1 · U12</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -20453,17 +20453,17 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>rvv-0030</t>
+          <t>rvv-0080</t>
         </is>
       </c>
     </row>
@@ -20472,58 +20472,58 @@
         <v>46368</v>
       </c>
       <c r="B334" s="5" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C334" s="5" t="n"/>
       <c r="D334" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
+          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker Svart · JU12</t>
+          <t>Jar · Jar Hvit · U12</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>rvv-0030</t>
+          <t>rvv-0080</t>
         </is>
       </c>
     </row>
@@ -20532,58 +20532,58 @@
         <v>46368</v>
       </c>
       <c r="B335" s="5" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C335" s="5" t="n"/>
       <c r="D335" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
+          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 2 · JU12</t>
+          <t>Jar · Jar Rød · U12</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>rvv-0030</t>
+          <t>rvv-0080</t>
         </is>
       </c>
     </row>
@@ -20592,58 +20592,58 @@
         <v>46368</v>
       </c>
       <c r="B336" s="5" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="C336" s="5" t="n"/>
       <c r="D336" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
+          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>Skien · Skien · JU12</t>
+          <t>Jutul · Jutul Grønn · U12</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>rvv-0030</t>
+          <t>rvv-0080</t>
         </is>
       </c>
     </row>
@@ -20652,23 +20652,23 @@
         <v>46368</v>
       </c>
       <c r="B337" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="C337" s="5" t="n"/>
       <c r="D337" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
+          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U12</t>
+          <t>Frisk Asker · Frisk Asker 1 · U8</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -20693,7 +20693,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -20703,7 +20703,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>rvv-0080</t>
+          <t>rvv-0015</t>
         </is>
       </c>
     </row>
@@ -20712,23 +20712,23 @@
         <v>46368</v>
       </c>
       <c r="B338" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="C338" s="5" t="n"/>
       <c r="D338" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E338" s="5" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
+          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -20738,22 +20738,22 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Jar · Jar Hvit · U12</t>
+          <t>Frisk Asker · Frisk Asker 3 · U8</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>rvv-0080</t>
+          <t>rvv-0015</t>
         </is>
       </c>
     </row>
@@ -20772,23 +20772,23 @@
         <v>46368</v>
       </c>
       <c r="B339" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="C339" s="5" t="n"/>
       <c r="D339" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E339" s="5" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
+          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -20798,22 +20798,22 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>Jar · Jar Rød · U12</t>
+          <t>Holmen · Holmen Hockey Hvit · U8</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -20823,7 +20823,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>rvv-0080</t>
+          <t>rvv-0015</t>
         </is>
       </c>
     </row>
@@ -20832,23 +20832,23 @@
         <v>46368</v>
       </c>
       <c r="B340" s="5" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="C340" s="5" t="n"/>
       <c r="D340" s="4" t="n">
         <v>46368</v>
       </c>
       <c r="E340" s="5" t="n">
-        <v>0.6736111111111112</v>
+        <v>0.7847222222222222</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>U8 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>U12 • Vert: Jutul • Lag: Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1 • RVV-ID: rvv-0080</t>
+          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -20858,32 +20858,32 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Grønn · U12</t>
+          <t>Jar · Jar Blå · U8</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>U8</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
           <t>Jutul</t>
         </is>
       </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>Jutul</t>
-        </is>
-      </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>rvv-0080</t>
+          <t>rvv-0015</t>
         </is>
       </c>
     </row>
@@ -20918,17 +20918,17 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U8</t>
+          <t>Jutul · Jutul Grønn · U8</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -20978,17 +20978,17 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 3 · U8</t>
+          <t>Jutul · Jutul Hvit · U8</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -21038,17 +21038,17 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Hvit · U8</t>
+          <t>Ringerike · Ringerike 2 · U8</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -21098,17 +21098,17 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>Jar · Jar Blå · U8</t>
+          <t>Tønsberg · Tønsberg · U8</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -21129,241 +21129,241 @@
     </row>
     <row r="345">
       <c r="A345" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="B345" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="C345" s="5" t="n"/>
       <c r="D345" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="E345" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
+          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Grønn · U8</t>
+          <t>Frisk Asker · Frisk Asker 1 · U10</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>rvv-0015</t>
+          <t>rvv-0073</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="B346" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="C346" s="5" t="n"/>
       <c r="D346" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="E346" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
+          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Hvit · U8</t>
+          <t>Holmen · Holmen Hockey Sort · U10</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>rvv-0015</t>
+          <t>rvv-0073</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="B347" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="C347" s="5" t="n"/>
       <c r="D347" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="E347" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
+          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 2 · U8</t>
+          <t>Jar · Jar Gul · U10</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
           <t>Ringerike</t>
         </is>
       </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t>U8</t>
-        </is>
-      </c>
-      <c r="M347" t="inlineStr">
-        <is>
-          <t>Jutul</t>
-        </is>
-      </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>rvv-0015</t>
+          <t>rvv-0073</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="B348" s="5" t="n">
-        <v>0.6770833333333334</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="C348" s="5" t="n"/>
       <c r="D348" s="4" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="E348" s="5" t="n">
-        <v>0.7847222222222222</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>U8 Turnering — Baerum ishall</t>
+          <t>U10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>U8 • Vert: Jutul • Lag: Jutul Hvit, Jutul Grønn, Frisk Asker 1, Holmen Hockey Hvit, Tønsberg, Ringerike 2, Frisk Asker 3, Jar Blå • RVV-ID: rvv-0015</t>
+          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Tønsberg · Tønsberg · U8</t>
+          <t>Jutul · Jutul Hvit · U10</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>rvv-0015</t>
+          <t>rvv-0073</t>
         </is>
       </c>
     </row>
@@ -21398,17 +21398,17 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U10</t>
+          <t>Kongsberg · Kongsberg · U10</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -21458,17 +21458,17 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Sort · U10</t>
+          <t>Ringerike · Ringerike 2 · U10</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -21499,51 +21499,51 @@
         <v>46369</v>
       </c>
       <c r="E351" s="5" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
+          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>Jar · Jar Gul · U10</t>
+          <t>Jutul · Jutul Rød · U12</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>rvv-0073</t>
+          <t>rvv-0091</t>
         </is>
       </c>
     </row>
@@ -21559,51 +21559,51 @@
         <v>46369</v>
       </c>
       <c r="E352" s="5" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
+          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Hvit · U10</t>
+          <t>Ringerike · Ringerike 1 · U12</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>rvv-0073</t>
+          <t>rvv-0091</t>
         </is>
       </c>
     </row>
@@ -21619,51 +21619,51 @@
         <v>46369</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
+          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Kongsberg · Kongsberg · U10</t>
+          <t>Ringerike · Ringerike 2 · U12</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>rvv-0073</t>
+          <t>rvv-0091</t>
         </is>
       </c>
     </row>
@@ -21679,51 +21679,51 @@
         <v>46369</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>U10 Turnering — Schjongshallen</t>
+          <t>U12 Turnering — Tonsberghallen</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>U10 • Vert: Ringerike • Lag: Ringerike 2, Frisk Asker 1, Jar Gul, Holmen Hockey Sort, Jutul Hvit, Kongsberg • RVV-ID: rvv-0073</t>
+          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 2 · U10</t>
+          <t>Tønsberg · Tønsberg Rød · U12</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>rvv-0073</t>
+          <t>rvv-0091</t>
         </is>
       </c>
     </row>
@@ -21732,58 +21732,58 @@
         <v>46369</v>
       </c>
       <c r="B355" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="C355" s="5" t="n"/>
       <c r="D355" s="4" t="n">
         <v>46369</v>
       </c>
       <c r="E355" s="5" t="n">
-        <v>0.4861111111111111</v>
+        <v>0.625</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
+          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Rød · U12</t>
+          <t>Frisk Asker · Frisk Asker Orange · JU12</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>rvv-0091</t>
+          <t>rvv-0030</t>
         </is>
       </c>
     </row>
@@ -21792,58 +21792,58 @@
         <v>46369</v>
       </c>
       <c r="B356" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="C356" s="5" t="n"/>
       <c r="D356" s="4" t="n">
         <v>46369</v>
       </c>
       <c r="E356" s="5" t="n">
-        <v>0.4861111111111111</v>
+        <v>0.625</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
+          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 1 · U12</t>
+          <t>Frisk Asker · Frisk Asker Svart · JU12</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>rvv-0091</t>
+          <t>rvv-0030</t>
         </is>
       </c>
     </row>
@@ -21852,33 +21852,33 @@
         <v>46369</v>
       </c>
       <c r="B357" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="C357" s="5" t="n"/>
       <c r="D357" s="4" t="n">
         <v>46369</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>0.4861111111111111</v>
+        <v>0.625</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
+          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 2 · U12</t>
+          <t>Ringerike · Ringerike 2 · JU12</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
@@ -21893,17 +21893,17 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>rvv-0091</t>
+          <t>rvv-0030</t>
         </is>
       </c>
     </row>
@@ -21912,58 +21912,58 @@
         <v>46369</v>
       </c>
       <c r="B358" s="5" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="C358" s="5" t="n"/>
       <c r="D358" s="4" t="n">
         <v>46369</v>
       </c>
       <c r="E358" s="5" t="n">
-        <v>0.4861111111111111</v>
+        <v>0.625</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>U12 Turnering — Tonsberghallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>U12 • Vert: Tønsberg • Lag: Ringerike 2, Jutul Rød, Ringerike 1, Tønsberg Rød • RVV-ID: rvv-0091</t>
+          <t>JU12 • Vert: Skien • Lag: Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart • RVV-ID: rvv-0030</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>Tønsberg · Tønsberg Rød · U12</t>
+          <t>Skien · Skien · JU12</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>rvv-0091</t>
+          <t>rvv-0030</t>
         </is>
       </c>
     </row>
@@ -61887,42 +61887,42 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JU12 Turnering — Skien ishall</t>
+          <t>U12 Turnering — Baerum ishall</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker, Ringerike</t>
+          <t>Jutul, Jar, Frisk Asker</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart</t>
+          <t>Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -61939,42 +61939,42 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U12 Turnering — Baerum ishall</t>
+          <t>JU10 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Schjongshallen</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Jutul, Jar, Frisk Asker</t>
+          <t>Ringerike, Jar, Frisk Asker</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Jutul Grønn, Jar Rød, Jar Hvit, Frisk Asker 1</t>
+          <t>Ringerike 1, Jar Hvit, Frisk Asker Svart, Jar Rød, Frisk Asker Orange</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -61991,7 +61991,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JU10 Turnering — Schjongshallen</t>
+          <t>U11 Turnering — Schjongshallen</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -62001,17 +62001,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -62021,12 +62021,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Ringerike, Jar, Frisk Asker</t>
+          <t>Ringerike, Frisk Asker, Tønsberg, Kongsberg, Sandefjord Penguins, Jar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Ringerike 1, Jar Hvit, Frisk Asker Svart, Jar Rød, Frisk Asker Orange</t>
+          <t>Ringerike Gul, Frisk Asker 3, Tønsberg Rød, Kongsberg, Sandefjord, Jar Gul</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -62038,47 +62038,47 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>12.12.2026</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U11 Turnering — Schjongshallen</t>
+          <t>JU12 Turnering — Skien ishall</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Schjongshallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Ringerike, Frisk Asker, Tønsberg, Kongsberg, Sandefjord Penguins, Jar</t>
+          <t>Skien, Frisk Asker, Ringerike</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Ringerike Gul, Frisk Asker 3, Tønsberg Rød, Kongsberg, Sandefjord, Jar Gul</t>
+          <t>Skien, Frisk Asker Orange, Ringerike 2, Frisk Asker Svart</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -67898,7 +67898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4c54761b2040299818ed893b7081e662bb9b249ce19ac891ba175a75bf89d7cb</t>
+          <t>899655001fbfce313ceddfded6afa4ced743fd714fce8d6471295350ee2b96a2</t>
         </is>
       </c>
     </row>

--- a/runs/legacy/season_plan_spond.xlsx
+++ b/runs/legacy/season_plan_spond.xlsx
@@ -552,58 +552,58 @@
         <v>46305</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="C2" s="5" t="n"/>
       <c r="D2" s="4" t="n">
         <v>46305</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
+          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 1 · U10</t>
+          <t>Holmen · Holmen Hockey Rød · U12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>rvv-0001</t>
+          <t>rvv-0004</t>
         </is>
       </c>
     </row>
@@ -612,58 +612,58 @@
         <v>46305</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="4" t="n">
         <v>46305</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
+          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Frisk Asker · Frisk Asker 3 · U10</t>
+          <t>Jutul · Jutul Grønn · U12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>rvv-0001</t>
+          <t>rvv-0004</t>
         </is>
       </c>
     </row>
@@ -672,58 +672,58 @@
         <v>46305</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="4" t="n">
         <v>46305</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
+          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Blå · U10</t>
+          <t>Kongsberg · Kongsberg · U12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Holmen Hockey Blå</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>Holmen</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Frisk Asker</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>rvv-0001</t>
+          <t>rvv-0004</t>
         </is>
       </c>
     </row>
@@ -732,58 +732,58 @@
         <v>46305</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="4" t="n">
         <v>46305</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>U10 Turnering — Askerhallen</t>
+          <t>U12 Turnering — Holmen ishall</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
+          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Askerhallen</t>
+          <t>Holmen ishall</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Jar · Jar Hvit · U10</t>
+          <t>Ringerike · Ringerike 1 · U12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>rvv-0001</t>
+          <t>rvv-0004</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Grønn · U10</t>
+          <t>Frisk Asker · Frisk Asker 1 · U10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 1 · U10</t>
+          <t>Frisk Asker · Frisk Asker 3 · U10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -919,31 +919,31 @@
         <v>46305</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Holmen · Holmen Hockey Rød · U12</t>
+          <t>Holmen · Holmen Hockey Blå · U10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -953,17 +953,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>rvv-0004</t>
+          <t>rvv-0001</t>
         </is>
       </c>
     </row>
@@ -979,51 +979,51 @@
         <v>46305</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Jutul · Jutul Grønn · U12</t>
+          <t>Jar · Jar Hvit · U10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>rvv-0004</t>
+          <t>rvv-0001</t>
         </is>
       </c>
     </row>
@@ -1039,51 +1039,51 @@
         <v>46305</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Kongsberg · Kongsberg · U12</t>
+          <t>Jutul · Jutul Grønn · U10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>rvv-0004</t>
+          <t>rvv-0001</t>
         </is>
       </c>
     </row>
@@ -1099,26 +1099,26 @@
         <v>46305</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6180555555555556</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>U12 Turnering — Holmen ishall</t>
+          <t>U10 Turnering — Askerhallen</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>U12 • Vert: Holmen • Lag: Holmen Hockey Rød, Jutul Grønn, Ringerike 1, Kongsberg • RVV-ID: rvv-0004</t>
+          <t>U10 • Vert: Frisk Asker • Lag: Frisk Asker 1, Frisk Asker 3, Jar Hvit, Holmen Hockey Blå, Ringerike 1, Jutul Grønn • RVV-ID: rvv-0001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Holmen ishall</t>
+          <t>Askerhallen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Ringerike · Ringerike 1 · U12</t>
+          <t>Ringerike · Ringerike 1 · U10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>rvv-0004</t>
+          <t>rvv-0001</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
         <v>46305</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>46305</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>46305</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>46305</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.625</v>
+        <v>0.6597222222222222</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3192,14 +3192,14 @@
         <v>46313</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C46" s="5" t="n"/>
       <c r="D46" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3252,14 +3252,14 @@
         <v>46313</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C47" s="5" t="n"/>
       <c r="D47" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3312,14 +3312,14 @@
         <v>46313</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3372,14 +3372,14 @@
         <v>46313</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C49" s="5" t="n"/>
       <c r="D49" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3432,14 +3432,14 @@
         <v>46313</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C50" s="5" t="n"/>
       <c r="D50" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3492,14 +3492,14 @@
         <v>46313</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="C51" s="5" t="n"/>
       <c r="D51" s="4" t="n">
         <v>46313</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.5763888888888888</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -58423,7 +58423,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -58470,12 +58470,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -58886,12 +58886,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -67898,7 +67898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>899655001fbfce313ceddfded6afa4ced743fd714fce8d6471295350ee2b96a2</t>
+          <t>733cff02efb97ac68d6b200f090ce013b8c03e21a44cd6ae1a2557211f672e8f</t>
         </is>
       </c>
     </row>

--- a/runs/legacy/season_plan_spond.xlsx
+++ b/runs/legacy/season_plan_spond.xlsx
@@ -54312,14 +54312,14 @@
         <v>46459</v>
       </c>
       <c r="B898" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C898" s="5" t="n"/>
       <c r="D898" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E898" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -54372,14 +54372,14 @@
         <v>46459</v>
       </c>
       <c r="B899" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C899" s="5" t="n"/>
       <c r="D899" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E899" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -54432,14 +54432,14 @@
         <v>46459</v>
       </c>
       <c r="B900" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C900" s="5" t="n"/>
       <c r="D900" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E900" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -54492,14 +54492,14 @@
         <v>46459</v>
       </c>
       <c r="B901" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C901" s="5" t="n"/>
       <c r="D901" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E901" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -54552,14 +54552,14 @@
         <v>46459</v>
       </c>
       <c r="B902" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C902" s="5" t="n"/>
       <c r="D902" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E902" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -54612,14 +54612,14 @@
         <v>46459</v>
       </c>
       <c r="B903" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C903" s="5" t="n"/>
       <c r="D903" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E903" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -54672,14 +54672,14 @@
         <v>46459</v>
       </c>
       <c r="B904" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C904" s="5" t="n"/>
       <c r="D904" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E904" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -54732,14 +54732,14 @@
         <v>46459</v>
       </c>
       <c r="B905" s="5" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="C905" s="5" t="n"/>
       <c r="D905" s="4" t="n">
         <v>46459</v>
       </c>
       <c r="E905" s="5" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -67201,12 +67201,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -67898,7 +67898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>733cff02efb97ac68d6b200f090ce013b8c03e21a44cd6ae1a2557211f672e8f</t>
+          <t>245e425ef51ba508c04a5ca42d5c20220ecafb0d9e4acf8d35e5e27b41ef89ee</t>
         </is>
       </c>
     </row>

--- a/runs/legacy/season_plan_spond.xlsx
+++ b/runs/legacy/season_plan_spond.xlsx
@@ -67898,7 +67898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>245e425ef51ba508c04a5ca42d5c20220ecafb0d9e4acf8d35e5e27b41ef89ee</t>
+          <t>f3f96bf6f522111c6518bbf4aac3ba1c51f5c8ede5372c3b411f50db197754cd</t>
         </is>
       </c>
     </row>
